--- a/data/Event_Data_NNA02VR-102.xlsx
+++ b/data/Event_Data_NNA02VR-102.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-10-2569 06:45</t>
+          <t>14-10-2569 08:29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,14 +468,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04-10-2569 13:35</t>
+          <t>10-10-2569 06:45</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,19 +485,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29-09-2569 21:36</t>
+          <t>04-10-2569 13:35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -507,19 +507,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29-09-2569 14:54</t>
+          <t>29-09-2569 21:36</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21-09-2569 05:08</t>
+          <t>29-09-2569 14:54</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -556,14 +556,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20-09-2569 16:02</t>
+          <t>21-09-2569 05:08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -573,19 +573,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>T/L กอไผ่แตะสายแรงสูง 185 PIC เฟส C บริเวณ บ.กุงโกน อ.ปลาปาก ห่าง R 15 กม.</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20-09-2569 14:46</t>
+          <t>20-09-2569 16:02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L กอไผ่แตะสายแรงสูง 185 PIC เฟส C บริเวณ บ.กุงโกน อ.ปลาปาก ห่าง R 15 กม.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08-09-2569 15:57</t>
+          <t>20-09-2569 14:46</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -629,7 +629,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28-08-2569 09:01</t>
+          <t>08-09-2569 15:57</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28-08-2569 00:59</t>
+          <t>28-08-2569 09:01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26-08-2569 08:05</t>
+          <t>28-08-2569 00:59</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,19 +683,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24-08-2569 13:21</t>
+          <t>26-08-2569 08:05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,19 +705,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>T/L งูขึ้น DF เฟส AB สาย 185SAC บ้านนายอ ห่าง R = 30 กม.</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20-08-2569 07:39</t>
+          <t>24-08-2569 13:21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้โน้มแตะสาย 185 A เฟส AB บ.นายอ ห่าง R6กม.จ่ายไฟ 08.10</t>
+          <t>T/L งูขึ้น DF เฟส AB สาย 185SAC บ้านนายอ ห่าง R = 30 กม.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18-08-2569 05:44</t>
+          <t>20-08-2569 07:39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,19 +749,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L กิ่งไม้โน้มแตะสาย 185 A เฟส AB บ.นายอ ห่าง R6กม.จ่ายไฟ 08.10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12-08-2569 05:58</t>
+          <t>18-08-2569 05:44</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06-08-2569 02:50</t>
+          <t>12-08-2569 05:58</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,19 +793,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 03.55</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03-08-2569 08:42</t>
+          <t>06-08-2569 02:50</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 03.55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28-07-2569 08:00</t>
+          <t>03-08-2569 08:42</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27-07-2569 04:16</t>
+          <t>28-07-2569 08:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19-07-2569 10:03</t>
+          <t>27-07-2569 04:16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -886,14 +886,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17-07-2569 08:58</t>
+          <t>19-07-2569 10:03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -908,14 +908,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>11-07-2569 18:45</t>
+          <t>17-07-2569 08:58</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>09-07-2569 22:57</t>
+          <t>11-07-2569 18:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -947,19 +947,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้เตะสาย 185A เฟส C บ้านนายอ ห่าง NNA02VS-106 = 3 กม.</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06-07-2569 06:43</t>
+          <t>09-07-2569 22:57</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -969,19 +969,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L กิ่งไม้เตะสาย 185A เฟส C บ้านนายอ ห่าง NNA02VS-106 = 3 กม.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>28-06-2569 13:22</t>
+          <t>06-07-2569 06:43</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T/L, เถาวัลย์พาดระบบจำหน่ายเฟส B (185A) บ้านโนนทัน ห่าง R = 15 กม. , จ่ายไฟ, 13.30</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26-06-2569 13:22</t>
+          <t>28-06-2569 13:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T/L ต้นไม้ล้มทับสาย 120A บ้านโนนคำหลัง ห่าง สฟฟ.ธพ. 20กม. เขตเรณู (ย้ายรับไฟ THA06)</t>
+          <t>T/L, เถาวัลย์พาดระบบจำหน่ายเฟส B (185A) บ้านโนนทัน ห่าง R = 15 กม. , จ่ายไฟ, 13.30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>21-06-2569 06:18</t>
+          <t>26-06-2569 13:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1040,14 +1040,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 06.28</t>
+          <t>T/L ต้นไม้ล้มทับสาย 120A บ้านโนนคำหลัง ห่าง สฟฟ.ธพ. 20กม. เขตเรณู (ย้ายรับไฟ THA06)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>20-06-2569 15:17</t>
+          <t>21-06-2569 06:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1062,14 +1062,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.34</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 06.28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15-06-2569 05:44</t>
+          <t>20-06-2569 15:17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1079,19 +1079,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>12-06-2569 18:35</t>
+          <t>15-06-2569 05:44</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1106,14 +1106,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31-05-2569 21:38</t>
+          <t>12-06-2569 18:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29-05-2569 02:09</t>
+          <t>31-05-2569 21:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>28-05-2569 16:52</t>
+          <t>29-05-2569 02:09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1167,19 +1167,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>T/L เถาวัลย์เลื้อแตะลูกถ้วย ก่อน NNA02VS-106 =200 ม. บ้านหนองยาว สาย 120A</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>19-05-2569 22:37</t>
+          <t>28-05-2569 16:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L เถาวัลย์เลื้อแตะลูกถ้วย ก่อน NNA02VS-106 =200 ม. บ้านหนองยาว สาย 120A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19-05-2569 00:33</t>
+          <t>19-05-2569 22:37</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1216,14 +1216,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>20-04-2569 08:48</t>
+          <t>19-05-2569 00:33</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1233,15 +1233,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>T/L</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>T/R</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>T/R ไม่ทราบสาเหตุ</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17-04-2569 13:20</t>
+          <t>20-04-2569 08:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1254,16 +1258,12 @@
           <t>T/L</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>T/L ไม่พบสาเหตุ</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>15-04-2569 15:45</t>
+          <t>17-04-2569 13:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1278,14 +1278,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้หักพาดสาย185A เฟส BC หน้าร.ร.วังไฮห่าง R1.5กม.จ่ายไฟ 15.53</t>
+          <t>T/L ไม่พบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>02-04-2569 07:14</t>
+          <t>15-04-2569 15:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1295,19 +1295,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L กิ่งไม้หักพาดสาย185A เฟส BC หน้าร.ร.วังไฮห่าง R1.5กม.จ่ายไฟ 15.53</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26-03-2569 11:06</t>
+          <t>02-04-2569 07:14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1317,19 +1317,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้หักพาดสายแรงสูง 185 PIC บ้านนาขาม ห่าง R = 17 กม. จ่ายไฟ 11.16</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>16-03-2569 10:44</t>
+          <t>26-03-2569 11:06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1344,14 +1344,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>T/L รถยนต์ชนเสาโคมไฟถนนล้มพาดสาย 120 A บริเวณ บ.หนองฮี ห่าง R 7 กม.</t>
+          <t>T/L กิ่งไม้หักพาดสายแรงสูง 185 PIC บ้านนาขาม ห่าง R = 17 กม. จ่ายไฟ 11.16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25-02-2569 05:40</t>
+          <t>16-03-2569 10:44</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1366,27 +1366,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>T/Lก่อไผ่หักพาดสาย 95A บ.นายอ ห่าง R.20กม.จ่ายไฟ 05.58</t>
+          <t>T/L รถยนต์ชนเสาโคมไฟถนนล้มพาดสาย 120 A บริเวณ บ.หนองฮี ห่าง R 7 กม.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>25-02-2569 05:40</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NNA02VR-102</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>T/L</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>T/Lก่อไผ่หักพาดสาย 95A บ.นายอ ห่าง R.20กม.จ่ายไฟ 05.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>28-01-2569 10:34</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NNA02VR-102</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>T/L</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NNA02VR-102</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>T/L</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>T/L ผู้รับจ้างตัดต้นไม้พาดสาย 120 ACSR เฟส AB บ.นายอห่าง R 9 กม. จ่ายไฟ 10.49</t>
         </is>
